--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jul-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15605167.2</v>
+        <v>16762.27</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>46868961.75</v>
+        <v>50344.22</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>40804637.3</v>
+        <v>43830.24</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6065382.68</v>
+        <v>6515.12</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5307842.85</v>
+        <v>5701.41</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>34104000</v>
+        <v>36632.76</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9298387</v>
+        <v>9987.85</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18314900.13</v>
+        <v>19672.92</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15875492.5</v>
+        <v>17052.64</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9513914.85</v>
+        <v>10219.36</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8943434.92</v>
+        <v>9606.58</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>23709231.9</v>
+        <v>25467.24</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10579619.4</v>
+        <v>11364.08</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10976000</v>
+        <v>11789.85</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5968370.52</v>
+        <v>6410.92</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7233960</v>
+        <v>7770.35</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7004982.6</v>
+        <v>7524.39</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>47574959</v>
+        <v>51102.57</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27493748.1</v>
+        <v>29532.37</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5318902.2</v>
+        <v>5713.29</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>50767785.95</v>
+        <v>54532.14</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>18168771.74</v>
+        <v>19515.96</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>16218389.46</v>
+        <v>17420.96</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5968361.7</v>
+        <v>6410.91</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>58713799.3</v>
+        <v>63067.34</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>35759811.1</v>
+        <v>38411.35</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8058181.9</v>
+        <v>8655.68</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9611956.4</v>
+        <v>10324.67</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>20475743.5</v>
+        <v>21993.99</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>34265986.16</v>
+        <v>36806.76</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9058839.720000001</v>
+        <v>9730.540000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8244981.3</v>
+        <v>8856.33</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5671086.1</v>
+        <v>6091.59</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>10245988.4</v>
+        <v>11005.71</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16941327.62</v>
+        <v>18197.5</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>23519571.74</v>
+        <v>25263.51</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9702559.58</v>
+        <v>10421.99</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7210832.2</v>
+        <v>7745.5</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9678638.9</v>
+        <v>10396.3</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>28598084.25</v>
+        <v>30718.59</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>186199865.74</v>
+        <v>200006.3</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>59163279.3</v>
+        <v>63550.15</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7651261.8</v>
+        <v>8218.59</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7437514</v>
+        <v>7988.99</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>14697481.4</v>
+        <v>15787.28</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>19717265.55</v>
+        <v>21179.27</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>36545971</v>
+        <v>39255.8</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11803714.55</v>
+        <v>12678.94</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8319445.55</v>
+        <v>8936.32</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7255441.9</v>
+        <v>7793.42</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>21497221.8</v>
+        <v>23091.21</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>16430768.2</v>
+        <v>17649.08</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>31312649.35</v>
+        <v>33634.43</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5956449.8</v>
+        <v>6398.11</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7592285.4</v>
+        <v>8155.24</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>13499098.2</v>
+        <v>14500.04</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5176665.75</v>
+        <v>5560.51</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>33338331.95</v>
+        <v>35810.32</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6641509</v>
+        <v>7133.97</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5968361.7</v>
+        <v>6410.91</v>
       </c>
     </row>
   </sheetData>
